--- a/WpfClient/Resources/ActPartsTemplate.xlsx
+++ b/WpfClient/Resources/ActPartsTemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thron\source\repos\RequestManagementSystem\WpfClient\Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thron\source\repos\Thron41k\RequestManagementSystem\WpfClient\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B37A01C1-0C0B-4106-884C-6BDAFEBA431A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94D99B90-A7FE-49D8-9528-001880F85D87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="734" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="734" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TDSheet" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
   <si>
     <t>Приложение № 19</t>
   </si>
@@ -125,6 +125,15 @@
   </si>
   <si>
     <t>Материально - ответственное лицо:</t>
+  </si>
+  <si>
+    <t>Объект (номенклатурная группа):</t>
+  </si>
+  <si>
+    <t>Вид дефекта</t>
+  </si>
+  <si>
+    <t>СОДЕРЖАНИЕ АВТОМОБИЛЬНОЙ ДОРОГИ АМУР И ИССО КМ 380+000 - КМ 741 + 775</t>
   </si>
 </sst>
 </file>
@@ -271,7 +280,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -330,50 +339,65 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -685,7 +709,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr defaultColWidth="10.1640625" defaultRowHeight="11.45" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.33203125" style="1" customWidth="1"/>
@@ -724,10 +748,10 @@
         <v>2</v>
       </c>
       <c r="E6" s="18"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
     </row>
     <row r="7" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I7" s="2" t="s">
@@ -736,25 +760,25 @@
     </row>
     <row r="8" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E8" s="3"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="35"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="27"/>
     </row>
     <row r="9" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E9" s="38" t="s">
+      <c r="E9" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="38"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
     </row>
     <row r="10" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="36"/>
-      <c r="I10" s="36"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
     </row>
     <row r="12" spans="1:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E12" s="4" t="s">
@@ -763,10 +787,10 @@
       <c r="F12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="37" t="s">
+      <c r="G12" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="37"/>
+      <c r="H12" s="29"/>
       <c r="I12" s="4" t="s">
         <v>8</v>
       </c>
@@ -780,249 +804,278 @@
       </c>
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="27"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
       <c r="I13" s="6"/>
     </row>
     <row r="14" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="28" t="s">
+      <c r="A14" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
     </row>
     <row r="15" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="28" t="s">
+      <c r="A15" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-    </row>
-    <row r="16" spans="1:9" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="29" t="s">
+      <c r="B15" s="33"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+    </row>
+    <row r="16" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="41" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="41"/>
+      <c r="C16" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="42"/>
+      <c r="I16" s="42"/>
+    </row>
+    <row r="17" spans="1:9" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="29"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="1" t="s">
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I16" s="9"/>
-    </row>
-    <row r="17" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="29" t="s">
+      <c r="I17" s="9"/>
+    </row>
+    <row r="18" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="26"/>
+      <c r="I18" s="25"/>
+    </row>
+    <row r="19" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="29"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="20"/>
-    </row>
-    <row r="18" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D18" s="28" t="s">
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+    </row>
+    <row r="20" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D20" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-    </row>
-    <row r="20" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="34" t="s">
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33"/>
+    </row>
+    <row r="22" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="34"/>
-      <c r="C20" s="7" t="s">
+      <c r="B22" s="39"/>
+      <c r="C22" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7" t="s">
+      <c r="D22" s="7"/>
+      <c r="E22" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F22" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G20" s="34" t="s">
+      <c r="G22" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="H20" s="34"/>
-      <c r="I20" s="34"/>
-    </row>
-    <row r="21" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="30"/>
-      <c r="B21" s="30"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="33"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="39"/>
     </row>
     <row r="23" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="A23" s="35"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="38"/>
     </row>
     <row r="25" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="11"/>
-      <c r="B30" s="10"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="G30" s="24"/>
-      <c r="H30" s="24"/>
-      <c r="I30" s="24"/>
-    </row>
-    <row r="31" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="1" t="s">
+    <row r="32" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="11"/>
+      <c r="B32" s="10"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="G32" s="40"/>
+      <c r="H32" s="40"/>
+      <c r="I32" s="40"/>
+    </row>
+    <row r="33" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D31" s="26" t="s">
+      <c r="D33" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="E31" s="26"/>
-      <c r="H31" s="1" t="s">
+      <c r="E33" s="31"/>
+      <c r="H33" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
+    <row r="34" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="3"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="25"/>
-      <c r="H33" s="25"/>
-      <c r="I33" s="25"/>
-    </row>
-    <row r="34" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="E34" s="26"/>
-      <c r="H34" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3"/>
-      <c r="B35" s="10"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="G35" s="24"/>
-      <c r="H35" s="24"/>
-      <c r="I35" s="24"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="43"/>
+      <c r="H35" s="43"/>
+      <c r="I35" s="43"/>
     </row>
     <row r="36" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B36" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D36" s="26" t="s">
+      <c r="D36" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="E36" s="26"/>
+      <c r="E36" s="31"/>
       <c r="H36" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="1" t="s">
+    <row r="37" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="3"/>
+      <c r="B37" s="10"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="G37" s="40"/>
+      <c r="H37" s="40"/>
+      <c r="I37" s="40"/>
+    </row>
+    <row r="38" spans="1:9" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B38" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="E38" s="31"/>
+      <c r="H38" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="3"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="24"/>
-      <c r="H39" s="24"/>
-      <c r="I39" s="24"/>
-    </row>
-    <row r="40" spans="1:9" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="1" t="s">
+    <row r="41" spans="1:9" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="3"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="40"/>
+      <c r="I41" s="40"/>
+    </row>
+    <row r="42" spans="1:9" ht="11.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B42" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D40" s="26" t="s">
+      <c r="D42" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="E40" s="26"/>
-      <c r="H40" s="1" t="s">
+      <c r="E42" s="31"/>
+      <c r="H42" s="1" t="s">
         <v>28</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="25">
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="G41:I41"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:I16"/>
     <mergeCell ref="F8:I8"/>
     <mergeCell ref="F10:I10"/>
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="F6:I6"/>
     <mergeCell ref="E9:I9"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="G39:I39"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D36:E36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="99" fitToHeight="0" orientation="portrait" r:id="rId1"/>
